--- a/artfynd/A 6113-2024 artfynd.xlsx
+++ b/artfynd/A 6113-2024 artfynd.xlsx
@@ -1075,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131231428</v>
+        <v>131231409</v>
       </c>
       <c r="B5" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,26 +1086,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1113,10 +1118,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448749</v>
+        <v>448671</v>
       </c>
       <c r="R5" t="n">
-        <v>6999249</v>
+        <v>6999217</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1151,13 +1156,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1176,14 +1185,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1201,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131231409</v>
+        <v>131231428</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,31 +1216,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1244,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448671</v>
+        <v>448749</v>
       </c>
       <c r="R6" t="n">
-        <v>6999217</v>
+        <v>6999249</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1282,17 +1281,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1311,9 +1306,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1604,7 +1604,7 @@
         <v>131231427</v>
       </c>
       <c r="B9" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 6113-2024 artfynd.xlsx
+++ b/artfynd/A 6113-2024 artfynd.xlsx
@@ -1075,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131231409</v>
+        <v>131231428</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,31 +1086,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1118,10 +1113,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448671</v>
+        <v>448749</v>
       </c>
       <c r="R5" t="n">
-        <v>6999217</v>
+        <v>6999249</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1156,17 +1151,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1185,9 +1176,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1205,10 +1201,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131231428</v>
+        <v>131231409</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,26 +1212,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1243,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448749</v>
+        <v>448671</v>
       </c>
       <c r="R6" t="n">
-        <v>6999249</v>
+        <v>6999217</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1281,13 +1282,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1306,14 +1311,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 6113-2024 artfynd.xlsx
+++ b/artfynd/A 6113-2024 artfynd.xlsx
@@ -1078,7 +1078,7 @@
         <v>131231428</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>131231427</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 6113-2024 artfynd.xlsx
+++ b/artfynd/A 6113-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131231410</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131231404</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>131231406</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>131231428</v>
       </c>
       <c r="B5" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>131231409</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>131231405</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>131231408</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>131231427</v>
       </c>
       <c r="B9" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>131231407</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6113-2024 artfynd.xlsx
+++ b/artfynd/A 6113-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131231410</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131231404</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>131231406</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131231428</v>
+        <v>131231409</v>
       </c>
       <c r="B5" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,26 +1086,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1113,10 +1118,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448749</v>
+        <v>448671</v>
       </c>
       <c r="R5" t="n">
-        <v>6999249</v>
+        <v>6999217</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1151,13 +1156,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1176,14 +1185,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1201,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131231409</v>
+        <v>131231428</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,31 +1216,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1244,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448671</v>
+        <v>448749</v>
       </c>
       <c r="R6" t="n">
-        <v>6999217</v>
+        <v>6999249</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1282,17 +1281,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1311,9 +1306,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1334,7 +1334,7 @@
         <v>131231405</v>
       </c>
       <c r="B7" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>131231408</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>131231427</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>131231407</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6113-2024 artfynd.xlsx
+++ b/artfynd/A 6113-2024 artfynd.xlsx
@@ -1075,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131231409</v>
+        <v>131231428</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,31 +1086,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1118,10 +1113,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448671</v>
+        <v>448749</v>
       </c>
       <c r="R5" t="n">
-        <v>6999217</v>
+        <v>6999249</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1156,17 +1151,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1185,9 +1176,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1205,10 +1201,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131231428</v>
+        <v>131231409</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,26 +1212,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1243,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448749</v>
+        <v>448671</v>
       </c>
       <c r="R6" t="n">
-        <v>6999249</v>
+        <v>6999217</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1281,13 +1282,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1306,14 +1311,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 6113-2024 artfynd.xlsx
+++ b/artfynd/A 6113-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131231410</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131231404</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>131231406</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131231428</v>
+        <v>131231409</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,26 +1086,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1113,10 +1118,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448749</v>
+        <v>448671</v>
       </c>
       <c r="R5" t="n">
-        <v>6999249</v>
+        <v>6999217</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1151,13 +1156,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1176,14 +1185,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1201,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131231409</v>
+        <v>131231428</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,31 +1216,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1244,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448671</v>
+        <v>448749</v>
       </c>
       <c r="R6" t="n">
-        <v>6999217</v>
+        <v>6999249</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1282,17 +1281,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1311,9 +1306,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1334,7 +1334,7 @@
         <v>131231405</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>131231408</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>131231427</v>
       </c>
       <c r="B9" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>131231407</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
